--- a/Documentation/Excel/Excel_fonction_octopus_diagram.xlsx
+++ b/Documentation/Excel/Excel_fonction_octopus_diagram.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Documents\Polytech\GPSE\4A\Projet\gyrobot\Documentation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470A0301-356B-4773-BB1B-CA27066EA65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8936D149-769A-4D1C-9DBB-A574745489E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="0" windowWidth="17325" windowHeight="15585" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
   </bookViews>
   <sheets>
     <sheet name="fct" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="115">
   <si>
     <t>Service function</t>
   </si>
@@ -139,9 +139,6 @@
     <t>Centered, above the wheel axis</t>
   </si>
   <si>
-    <t>&lt; 1 kg</t>
-  </si>
-  <si>
     <t>20 cm</t>
   </si>
   <si>
@@ -301,9 +298,6 @@
     <t>Stand load capacity</t>
   </si>
   <si>
-    <t>&gt; 1kg</t>
-  </si>
-  <si>
     <t>Easy disassembly (FC7) : The robot must be easy and safe to disassemble</t>
   </si>
   <si>
@@ -361,7 +355,16 @@
     <t>+ 2</t>
   </si>
   <si>
-    <t>&lt; 3min</t>
+    <t>Colored</t>
+  </si>
+  <si>
+    <t>&lt; 1,5 kg</t>
+  </si>
+  <si>
+    <t>&gt; 1,5 kg</t>
+  </si>
+  <si>
+    <t>&gt; 3min</t>
   </si>
 </sst>
 </file>
@@ -937,28 +940,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -971,6 +956,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1351,7 +1354,7 @@
   <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="91.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="91.7109375" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -1359,7 +1362,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1373,7 +1376,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1383,13 +1386,13 @@
         <v>30</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="12"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>28</v>
@@ -1399,7 +1402,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1413,7 +1416,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="12"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1425,7 +1428,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="12"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
@@ -1437,7 +1440,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="12"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="3" t="s">
         <v>32</v>
       </c>
@@ -1449,21 +1452,21 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="12"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -1471,107 +1474,107 @@
         <v>37</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="16"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="12"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D11" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="12"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="D13" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="18"/>
+      <c r="B15" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="16"/>
-      <c r="B15" s="20" t="s">
+      <c r="B16" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="15" t="s">
+      <c r="C16" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="18"/>
+      <c r="B17" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C17" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="16"/>
-      <c r="B17" s="6" t="s">
+      <c r="D17" s="15" t="s">
         <v>110</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1582,108 +1585,108 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="18"/>
+      <c r="B20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="16"/>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="18"/>
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="16"/>
-      <c r="B22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D22" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="18"/>
+      <c r="B24" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="16"/>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="15" t="s">
+      <c r="B25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="18"/>
+      <c r="B26" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="16"/>
-      <c r="B26" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>7</v>
@@ -1693,113 +1696,113 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="19"/>
+      <c r="B28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="17"/>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="19"/>
+      <c r="B29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="17"/>
-      <c r="B29" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="18"/>
+      <c r="B30" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="16"/>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="18" t="s">
+      <c r="C31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1">
+      <c r="A32" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1">
-      <c r="A32" s="15" t="s">
+      <c r="C32" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="18"/>
+      <c r="B33" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="16"/>
-      <c r="B33" s="3" t="s">
+      <c r="D33" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="15" t="s">
+      <c r="C34" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="18"/>
+      <c r="B35" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="16"/>
-      <c r="B35" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>7</v>
@@ -1809,7 +1812,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="16" t="s">
         <v>17</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -1823,33 +1826,33 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="12"/>
+      <c r="A37" s="16"/>
       <c r="B37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="3" t="s">
         <v>22</v>
       </c>
@@ -1857,39 +1860,39 @@
         <v>0.8</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="16"/>
+      <c r="B41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="12"/>
-      <c r="B41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="16"/>
+      <c r="B42" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="12"/>
-      <c r="B42" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>24</v>
@@ -1899,11 +1902,11 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="C43" s="4">
         <v>0.8</v>
@@ -1913,24 +1916,24 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="12"/>
+      <c r="A44" s="16"/>
       <c r="B44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="16"/>
+      <c r="B45" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="12"/>
-      <c r="B45" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>36</v>
@@ -1938,39 +1941,39 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="12" t="s">
+      <c r="B47" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D47" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="12"/>
+      <c r="A48" s="16"/>
       <c r="B48" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>36</v>
@@ -1978,13 +1981,8 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A40:A42"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A9"/>
@@ -1994,9 +1992,14 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A40:A42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
